--- a/input/assets/loinc-valuesets.xlsx
+++ b/input/assets/loinc-valuesets.xlsx
@@ -4,6 +4,7 @@
   <sheets>
     <sheet name="VS-CoreDataset" sheetId="1" r:id="rId1"/>
     <sheet name="VS-ExtendedDataset" sheetId="2" r:id="rId2"/>
+    <sheet name="ConceptMap 歸一" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -51,6 +52,10 @@
     <col min="1" max="1" width="55" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="65" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -69,6 +74,26 @@
           <t xml:space="preserve">Display Name</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">層級 Tier</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">歸一至 Normalizes To</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">equivalence</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">備註 Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -86,6 +111,14 @@
           <t xml:space="preserve">Cholesterol [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -103,6 +136,26 @@
           <t xml:space="preserve">Cholesterol [Mass or Moles/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2093-3　Cholesterol [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrower</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 質量/莫耳濃度未指定之變異碼（tx 確認非全血法）</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -120,6 +173,14 @@
           <t xml:space="preserve">Fasting glucose [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -137,6 +198,26 @@
           <t xml:space="preserve">Glucose [Mass/volume] in Blood</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1558-6　Fasting glucose [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 全血血糖</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -154,6 +235,26 @@
           <t xml:space="preserve">Glucose [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1558-6　Fasting Glucose [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrower</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 一般血糖（未指定空腹；tx 確認非「post fasting」）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -171,6 +272,14 @@
           <t xml:space="preserve">Triglyceride [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -188,6 +297,26 @@
           <t xml:space="preserve">Triglyceride [Mass/volume] in Blood</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2571-8　Triglyceride [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 全血法</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -205,6 +334,14 @@
           <t xml:space="preserve">Cholesterol in HDL [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -222,6 +359,14 @@
           <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -239,6 +384,26 @@
           <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by calculation</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2089-1　Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 計算法</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -256,6 +421,26 @@
           <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by Direct assay</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2089-1　Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 直接法舊碼</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -273,6 +458,14 @@
           <t xml:space="preserve">Creatinine [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -290,6 +483,26 @@
           <t xml:space="preserve">Creatinine [Mass/volume] in Blood</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2160-0　Creatinine [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 全血法</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -307,6 +520,14 @@
           <t xml:space="preserve">Protein [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -324,6 +545,14 @@
           <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -341,6 +570,26 @@
           <t xml:space="preserve">Protein [Presence] in Urine by Automated test strip</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 試紙變異碼</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -358,6 +607,14 @@
           <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -375,6 +632,26 @@
           <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5196-1　Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 血清定性(原22326-3 經tx驗證實為 HCV 5-1-1 Ab，已更正)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -392,6 +669,26 @@
           <t xml:space="preserve">Hepatitis B virus surface Ag [Units/volume] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5196-1　Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 免疫法</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -409,6 +706,14 @@
           <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -424,6 +729,26 @@
       <c r="C22" t="inlineStr">
         <is>
           <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13955-0　Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 血清通用碼（原 47365-2 為捐血者篩檢情境碼，不適用一般健檢，已更正）</t>
         </is>
       </c>
     </row>
@@ -437,6 +762,10 @@
     <col min="1" max="1" width="55" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="65" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,6 +784,26 @@
           <t xml:space="preserve">Display Name</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">層級 Tier</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">歸一至 Normalizes To</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">equivalence</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">備註 Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,6 +821,18 @@
           <t xml:space="preserve">EKG study</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">心電圖</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -489,6 +850,18 @@
           <t xml:space="preserve">Sodium [Moles/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鈉</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -506,6 +879,18 @@
           <t xml:space="preserve">Potassium [Moles/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鉀</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -523,6 +908,18 @@
           <t xml:space="preserve">Chloride [Moles/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">氯（v1.1 補齊電解質三項）</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -540,6 +937,18 @@
           <t xml:space="preserve">Urea nitrogen [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUN（腎功能/脫水評估）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -557,6 +966,18 @@
           <t xml:space="preserve">Specific gravity of Urine by Refractometry</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">尿比重（脫水評估）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -574,6 +995,18 @@
           <t xml:space="preserve">Pure tone air conduction threshold audiometry panel</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panel (重複收錄供查詢)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -591,6 +1024,14 @@
           <t xml:space="preserve">Hearing threshold Ear - left --500 Hz</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -608,6 +1049,14 @@
           <t xml:space="preserve">Hearing threshold Ear - left --1000 Hz</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -625,6 +1074,14 @@
           <t xml:space="preserve">Hearing threshold Ear - left --2000 Hz</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -642,6 +1099,14 @@
           <t xml:space="preserve">Hearing threshold Ear - left --3000 Hz</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -659,6 +1124,14 @@
           <t xml:space="preserve">Hearing threshold Ear - left --4000 Hz</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -676,6 +1149,14 @@
           <t xml:space="preserve">Hearing threshold Ear - left --6000 Hz</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -693,6 +1174,14 @@
           <t xml:space="preserve">Hearing threshold Ear - left --8000 Hz</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -710,6 +1199,14 @@
           <t xml:space="preserve">Hearing threshold Ear - right --500 Hz</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -727,6 +1224,14 @@
           <t xml:space="preserve">Hearing threshold Ear - right --1000 Hz</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -744,6 +1249,14 @@
           <t xml:space="preserve">Hearing threshold Ear - right --2000 Hz</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -761,6 +1274,14 @@
           <t xml:space="preserve">Hearing threshold Ear - right --3000 Hz</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -778,6 +1299,14 @@
           <t xml:space="preserve">Hearing threshold Ear - right --4000 Hz</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -795,6 +1324,14 @@
           <t xml:space="preserve">Hearing threshold Ear - right --6000 Hz</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -812,6 +1349,14 @@
           <t xml:space="preserve">Hearing threshold Ear - right --8000 Hz</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -829,6 +1374,14 @@
           <t xml:space="preserve">Erythrocytes [#/volume] in Blood by Automated count</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -846,6 +1399,14 @@
           <t xml:space="preserve">Leukocytes [#/volume] in Blood by Automated count</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -863,6 +1424,14 @@
           <t xml:space="preserve">Platelets [#/volume] in Blood by Automated count</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -880,6 +1449,14 @@
           <t xml:space="preserve">Hemoglobin [Mass/volume] in Blood</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -897,6 +1474,14 @@
           <t xml:space="preserve">Hematocrit [Volume Fraction] of Blood by Automated count</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -914,6 +1499,14 @@
           <t xml:space="preserve">Neutrophils/Leukocytes in Blood by Automated count</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -931,6 +1524,14 @@
           <t xml:space="preserve">Lymphocytes/Leukocytes in Blood by Automated count</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -948,6 +1549,18 @@
           <t xml:space="preserve">Thyrotropin [Units/volume] in Serum or Plasma by Detection limit &lt;= 0.005 mIU/L</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSH（輻射甲狀腺監測）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -965,6 +1578,18 @@
           <t xml:space="preserve">Thyroxine (T4) free [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free T4（輻射甲狀腺監測）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -982,6 +1607,18 @@
           <t xml:space="preserve">XR Bones.long Survey</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">長骨/關節 X 光（減壓性骨壞死）</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -999,6 +1636,18 @@
           <t xml:space="preserve">Forced vital capacity [Volume] Respiratory system by Spirometry</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FVC (Preferred：方法通用碼)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1016,6 +1665,18 @@
           <t xml:space="preserve">FEV1</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEV1（正確碼）</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1033,6 +1694,18 @@
           <t xml:space="preserve">FEV1/FVC</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEV1/FVC</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1050,6 +1723,18 @@
           <t xml:space="preserve">Lead [Mass/volume] in Venous blood</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">血中鉛 Preferred（v20260726 由 5671-3 改列；5671-3 之 LOINC 狀態為 DISCOURAGED）</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1067,6 +1752,26 @@
           <t xml:space="preserve">Lead [Mass/volume] in Blood</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77307-7　Lead [Mass/volume] in Venous blood</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：檢體未指定之舊碼（LOINC DISCOURAGED），經 ConceptMap 歸一至 77307-7</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1084,6 +1789,14 @@
           <t xml:space="preserve">Lead [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1101,6 +1814,26 @@
           <t xml:space="preserve">Lead [Mass/volume] in Specimen</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77307-7　Lead [Mass/volume] in Venous blood</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 血鉛檢體泛稱碼（院內 LIS 實際報告碼）；經 ConceptMap 歸一至 77307-7（#relatedto，檢體不同）</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1118,6 +1851,14 @@
           <t xml:space="preserve">Coproporphyrin [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1135,6 +1876,14 @@
           <t xml:space="preserve">Delta aminolevulinate [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1152,6 +1901,18 @@
           <t xml:space="preserve">XR Chest 2 Views</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">胸部 X 光（2 views，塵肺症）</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1169,6 +1930,18 @@
           <t xml:space="preserve">XR Chest PA upright</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">胸部 X 光（單張 PA，附表九一般大片）</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1186,6 +1959,18 @@
           <t xml:space="preserve">Gamma glutamyl transferase [Enzymatic activity/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">γ-GT（肝功能，v1.1 明列）</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1203,6 +1988,18 @@
           <t xml:space="preserve">Hippurate [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">馬尿酸（甲苯）</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1220,6 +2017,18 @@
           <t xml:space="preserve">Para methylhippurate [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">甲基馬尿酸（二甲苯）</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1237,6 +2046,18 @@
           <t xml:space="preserve">Mandelate [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">扁桃酸（苯乙烯）</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1254,6 +2075,18 @@
           <t xml:space="preserve">Trichloroacetate [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三氯乙酸（三氯乙烯/四氯乙烯）</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1271,6 +2104,18 @@
           <t xml:space="preserve">2,5-Hexanedione [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,5-己二酮（正己烷）</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1288,6 +2133,18 @@
           <t xml:space="preserve">Phenol [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">酚（苯）</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1305,6 +2162,18 @@
           <t xml:space="preserve">Methyl formamide [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N-甲基甲醯胺（DMF）</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1322,6 +2191,18 @@
           <t xml:space="preserve">Thiazolidine-2-Thione-4-Carboxylic acid [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TTCA（二硫化碳）</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1339,6 +2220,14 @@
           <t xml:space="preserve">Arsenic [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1356,6 +2245,14 @@
           <t xml:space="preserve">Cadmium [Mass/volume] in Blood</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1373,6 +2270,14 @@
           <t xml:space="preserve">Cadmium [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1390,6 +2295,14 @@
           <t xml:space="preserve">Cadmium/Creatinine [Mass Ratio] in Urine</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1407,6 +2320,14 @@
           <t xml:space="preserve">Chromium [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1424,6 +2345,14 @@
           <t xml:space="preserve">Chromium [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1441,6 +2370,14 @@
           <t xml:space="preserve">Chromium/Creatinine [Mass Ratio] in Urine</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1458,6 +2395,14 @@
           <t xml:space="preserve">Nickel [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1475,6 +2420,14 @@
           <t xml:space="preserve">Mercury [Mass/volume] in Blood</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1492,6 +2445,14 @@
           <t xml:space="preserve">Mercury [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E62"/>
+      <c r="F62"/>
+      <c r="G62"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1509,6 +2470,14 @@
           <t xml:space="preserve">trans,trans-Muconic acid [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E63"/>
+      <c r="F63"/>
+      <c r="G63"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1526,6 +2495,14 @@
           <t xml:space="preserve">4,4'-Methylene bis(2-Chloroaniline) [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E64"/>
+      <c r="F64"/>
+      <c r="G64"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1543,6 +2520,14 @@
           <t xml:space="preserve">Formaldehyde [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E65"/>
+      <c r="F65"/>
+      <c r="G65"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1560,6 +2545,14 @@
           <t xml:space="preserve">Benzidine [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E66"/>
+      <c r="F66"/>
+      <c r="G66"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1577,6 +2570,14 @@
           <t xml:space="preserve">Manganese [Mass/volume] in Blood</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E67"/>
+      <c r="F67"/>
+      <c r="G67"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1594,6 +2595,14 @@
           <t xml:space="preserve">Manganese [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E68"/>
+      <c r="F68"/>
+      <c r="G68"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1611,6 +2620,18 @@
           <t xml:space="preserve">Manganese [Moles/volume] in Urine</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E69"/>
+      <c r="F69"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29 JOB-01 批3 Q2-1：官方為莫耳（舊標質量有誤，碼本身為莫耳）；院方以 µg/L 質量報告，質量碼見下 5684-6</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1628,6 +2649,18 @@
           <t xml:space="preserve">Manganese [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E70"/>
+      <c r="F70"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">院方所用之質量碼（µg/L, Q2-1）；WebSearch 取自 loinc.org，經 CI $lookup 覆核</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1645,6 +2678,18 @@
           <t xml:space="preserve">Fluoride [Moles/volume] in Urine</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E71"/>
+      <c r="F71"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29 JOB-01 批2：官方為莫耳濃度（Q2-2）；質量碼見下 5650-7</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1662,6 +2707,18 @@
           <t xml:space="preserve">Fluoride [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E72"/>
+      <c r="F72"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29 JOB-01 批3：批2 誤薦之 5605-7 不存在於 LOINC，正確質量碼為 5650-7（mg/L, Q2-2）；WebSearch 取自 loinc.org，經 CI $lookup 覆核</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1679,6 +2736,14 @@
           <t xml:space="preserve">Phosphate [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E73"/>
+      <c r="F73"/>
+      <c r="G73"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1696,6 +2761,14 @@
           <t xml:space="preserve">XR Mandible Views</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E74"/>
+      <c r="F74"/>
+      <c r="G74"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1713,6 +2786,14 @@
           <t xml:space="preserve">Paraquat [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E75"/>
+      <c r="F75"/>
+      <c r="G75"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1730,6 +2811,14 @@
           <t xml:space="preserve">Indium [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E76"/>
+      <c r="F76"/>
+      <c r="G76"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1747,6 +2836,14 @@
           <t xml:space="preserve">Indium [Mass/volume] in Blood</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E77"/>
+      <c r="F77"/>
+      <c r="G77"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1764,6 +2861,14 @@
           <t xml:space="preserve">Cobalt [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E78"/>
+      <c r="F78"/>
+      <c r="G78"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1781,6 +2886,14 @@
           <t xml:space="preserve">Cobalt [Mass/volume] in Blood</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E79"/>
+      <c r="F79"/>
+      <c r="G79"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1798,6 +2911,14 @@
           <t xml:space="preserve">Bromide [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E80"/>
+      <c r="F80"/>
+      <c r="G80"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1815,6 +2936,14 @@
           <t xml:space="preserve">Bromide [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E81"/>
+      <c r="F81"/>
+      <c r="G81"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1832,6 +2961,14 @@
           <t xml:space="preserve">Acetylcholinesterase [Enzymatic activity/volume] in Red Blood Cells</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E82"/>
+      <c r="F82"/>
+      <c r="G82"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1849,6 +2986,14 @@
           <t xml:space="preserve">Cholinesterase [Enzymatic activity/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E83"/>
+      <c r="F83"/>
+      <c r="G83"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1866,6 +3011,18 @@
           <t xml:space="preserve">Salmonella and Shigella sp identified in Stool by Organism specific culture</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E84"/>
+      <c r="F84"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29 JOB-01 批2：批1 顯示名多轉抄一個「sp」，依 display-verification-report.csv 官方字串更正</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1883,6 +3040,14 @@
           <t xml:space="preserve">Amphetamines [Presence] in Urine</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E85"/>
+      <c r="F85"/>
+      <c r="G85"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1900,6 +3065,14 @@
           <t xml:space="preserve">Opiates [Presence] in Urine</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="G86"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1917,6 +3090,14 @@
           <t xml:space="preserve">Benzodiazepines [Presence] in Urine</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1934,6 +3115,14 @@
           <t xml:space="preserve">Ketamine [Presence] in Urine</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E88"/>
+      <c r="F88"/>
+      <c r="G88"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1951,6 +3140,14 @@
           <t xml:space="preserve">Methylenedioxymethamphetamine [Presence] in Urine</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E89"/>
+      <c r="F89"/>
+      <c r="G89"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1968,6 +3165,18 @@
           <t xml:space="preserve">Alpha-1-Fetoprotein [Moles/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E90"/>
+      <c r="F90"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29 JOB-01 批2：官方為莫耳濃度（Q2-3）；院內以 ng/mL 質量報告，質量碼見 1834-1（通用）與 53962-7（免疫分析法）</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1985,6 +3194,18 @@
           <t xml:space="preserve">Alpha-1-fetoprotein.tumor marker [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E91"/>
+      <c r="F91"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">檢驗醫學部所用之質量碼（ng/mL, Q2-3）；CI 查證官方為腫瘤標記型 AFP 質量碼，適用於本節癌症篩檢情境，顯示名已依官方更正</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2002,6 +3223,14 @@
           <t xml:space="preserve">Carcinoembryonic Ag [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E92"/>
+      <c r="F92"/>
+      <c r="G92"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2019,6 +3248,14 @@
           <t xml:space="preserve">Prostate specific Ag [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E93"/>
+      <c r="F93"/>
+      <c r="G93"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2036,6 +3273,14 @@
           <t xml:space="preserve">Prostate Specific Ag Free [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E94"/>
+      <c r="F94"/>
+      <c r="G94"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2053,6 +3298,14 @@
           <t xml:space="preserve">proPSA isoform 2 [Mass/volume] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E95"/>
+      <c r="F95"/>
+      <c r="G95"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2070,6 +3323,14 @@
           <t xml:space="preserve">Prostate health index in Serum or Plasma by calculation</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E96"/>
+      <c r="F96"/>
+      <c r="G96"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2087,6 +3348,14 @@
           <t xml:space="preserve">Cancer Ag 125 [Units/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E97"/>
+      <c r="F97"/>
+      <c r="G97"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2104,6 +3373,26 @@
           <t xml:space="preserve">Cancer Ag 125 [Units/volume] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10334-1　Cancer Ag 125 [Units/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: CA-125 免疫法具名碼；經 ConceptMap 歸一至 10334-1</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2121,6 +3410,26 @@
           <t xml:space="preserve">Carcinoembryonic Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2039-6　Carcinoembryonic Ag [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: CEA 免疫法具名碼；經 ConceptMap 歸一至 2039-6</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2138,6 +3447,14 @@
           <t xml:space="preserve">Cancer Ag 19-9 [Units/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E100"/>
+      <c r="F100"/>
+      <c r="G100"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2155,6 +3472,14 @@
           <t xml:space="preserve">Cancer Ag 19-9 [Units/volume] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2172,6 +3497,14 @@
           <t xml:space="preserve">Cancer Ag 15-3 [Units/volume] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2189,6 +3522,14 @@
           <t xml:space="preserve">Prostate specific Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2206,6 +3547,14 @@
           <t xml:space="preserve">Alpha-1-fetoprotein [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2223,6 +3572,14 @@
           <t xml:space="preserve">Squamous cell carcinoma Ag [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2240,6 +3597,14 @@
           <t xml:space="preserve">IgE [Units/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2257,6 +3622,18 @@
           <t xml:space="preserve">Epstein Barr virus capsid IgA Ab [Titer] in Serum by Immunofluorescence</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29 JOB-01 批3 Q4-2：顯示名為官方（原標 [Presence] 有誤；LOINC FSN=SemiQn/IF）。院方雖以 EIA 定量報告，惟 LOINC 無 capsid IgA [Units/volume] by Immunoassay 碼；經使用者裁示（2026-07-29）保留本 VCA IgA IFA 效價碼，方法/量表落差為已知並接受之 LOINC 缺口</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2274,6 +3651,14 @@
           <t xml:space="preserve">Lipoprotein A [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E108"/>
+      <c r="F108"/>
+      <c r="G108"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2291,6 +3676,14 @@
           <t xml:space="preserve">Apolipoprotein A-I [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E109"/>
+      <c r="F109"/>
+      <c r="G109"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2308,6 +3701,14 @@
           <t xml:space="preserve">Apolipoprotein B [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2325,6 +3726,14 @@
           <t xml:space="preserve">Natriuretic peptide.B prohormone N-Terminal [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2342,6 +3751,14 @@
           <t xml:space="preserve">Nuclear Ab [Presence] in Serum by Immunofluorescence</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E112"/>
+      <c r="F112"/>
+      <c r="G112"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2359,6 +3776,14 @@
           <t xml:space="preserve">Rheumatoid factor [Units/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2376,6 +3801,14 @@
           <t xml:space="preserve">Cytokeratin 19 [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E114"/>
+      <c r="F114"/>
+      <c r="G114"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2393,6 +3826,14 @@
           <t xml:space="preserve">MG Breast Screening</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E115"/>
+      <c r="F115"/>
+      <c r="G115"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2410,6 +3851,18 @@
           <t xml:space="preserve">DBT Brst Screening</t>
         </is>
       </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E116"/>
+      <c r="F116"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3D乳房斷層攝影</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2427,6 +3880,14 @@
           <t xml:space="preserve">MR Brain</t>
         </is>
       </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E117"/>
+      <c r="F117"/>
+      <c r="G117"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2444,6 +3905,14 @@
           <t xml:space="preserve">CT Chest Screening WO contr</t>
         </is>
       </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E118"/>
+      <c r="F118"/>
+      <c r="G118"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2461,6 +3930,14 @@
           <t xml:space="preserve">CT Chest Screening</t>
         </is>
       </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E119"/>
+      <c r="F119"/>
+      <c r="G119"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2478,6 +3955,14 @@
           <t xml:space="preserve">PT+CT Whole body Tum loc W 18F-FDG IV</t>
         </is>
       </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="G120"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2495,6 +3980,14 @@
           <t xml:space="preserve">CTA Hrt+CA W contr IV</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E121"/>
+      <c r="F121"/>
+      <c r="G121"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2512,6 +4005,18 @@
           <t xml:space="preserve">EGD Study</t>
         </is>
       </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">胃鏡檢查</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2529,6 +4034,18 @@
           <t xml:space="preserve">Colonoscopy Study</t>
         </is>
       </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E123"/>
+      <c r="F123"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大腸鏡檢查</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2546,6 +4063,18 @@
           <t xml:space="preserve">US Abdomen</t>
         </is>
       </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E124"/>
+      <c r="F124"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">腹部超音波</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2563,6 +4092,18 @@
           <t xml:space="preserve">US Carotid aa</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E125"/>
+      <c r="F125"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">頸動脈超音波</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2580,6 +4121,18 @@
           <t xml:space="preserve">US Thyroid</t>
         </is>
       </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E126"/>
+      <c r="F126"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">甲狀腺超音波</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2597,6 +4150,18 @@
           <t xml:space="preserve">DXA Skeletal Sys Views for BMD</t>
         </is>
       </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E127"/>
+      <c r="F127"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雙能量X光骨密度儀(DEXA)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2614,6 +4179,14 @@
           <t xml:space="preserve">Variant lymphocytes/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E128"/>
+      <c r="F128"/>
+      <c r="G128"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2631,6 +4204,14 @@
           <t xml:space="preserve">Plasma cells/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E129"/>
+      <c r="F129"/>
+      <c r="G129"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2648,6 +4229,14 @@
           <t xml:space="preserve">Nucleated erythrocytes/Leukocytes [Ratio] in Blood</t>
         </is>
       </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E130"/>
+      <c r="F130"/>
+      <c r="G130"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2665,6 +4254,14 @@
           <t xml:space="preserve">Blasts/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E131"/>
+      <c r="F131"/>
+      <c r="G131"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2682,6 +4279,14 @@
           <t xml:space="preserve">Eosinophils/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E132"/>
+      <c r="F132"/>
+      <c r="G132"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2699,6 +4304,26 @@
           <t xml:space="preserve">Leukocytes [#/volume] in Blood</t>
         </is>
       </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6690-2　Leukocytes [#/volume] in Blood by Automated count</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrower</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: WBC unspecified</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2716,6 +4341,14 @@
           <t xml:space="preserve">Lymphocytes/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E134"/>
+      <c r="F134"/>
+      <c r="G134"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2733,6 +4366,14 @@
           <t xml:space="preserve">Monocytes/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E135"/>
+      <c r="F135"/>
+      <c r="G135"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2750,6 +4391,14 @@
           <t xml:space="preserve">Myelocytes/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E136"/>
+      <c r="F136"/>
+      <c r="G136"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2767,6 +4416,18 @@
           <t xml:space="preserve">Segmented neutrophils/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E137"/>
+      <c r="F137"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-26 更正 display（原誤標 Hypersegmented）；⚠️ 待確認：如確需「過度分葉核」項目應另加 30450-1</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2784,6 +4445,26 @@
           <t xml:space="preserve">Band form neutrophils/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">770-8　Neutrophils/Leukocytes in Blood by Automated count</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 嗜中性球帶狀核手工計數；經 ConceptMap 歸一至 770-8（#relatedto，不同具體方法）。2026-07-26 更正 display（原誤標為總嗜中性球手工計數）</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2801,6 +4482,18 @@
           <t xml:space="preserve">Neutrophils/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E139"/>
+      <c r="F139"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-26 更正 display（原誤標 segmented）；⚠️ 待確認：如確需「手工計數」版本應另加 23761-0</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2818,6 +4511,26 @@
           <t xml:space="preserve">Platelets [#/volume] in Blood</t>
         </is>
       </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777-3　Platelets [#/volume] in Blood by Automated count</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrower</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: Plt Automated</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2835,6 +4548,14 @@
           <t xml:space="preserve">Promyelocytes/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E141"/>
+      <c r="F141"/>
+      <c r="G141"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2852,6 +4573,26 @@
           <t xml:space="preserve">MCH [Entitic mass]</t>
         </is>
       </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">785-6　MCH [Entitic mass] by Automated count</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrower</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: MCH (full name)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2869,6 +4610,14 @@
           <t xml:space="preserve">Metamyelocytes/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E143"/>
+      <c r="F143"/>
+      <c r="G143"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2886,6 +4635,14 @@
           <t xml:space="preserve">Basophils/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E144"/>
+      <c r="F144"/>
+      <c r="G144"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2903,6 +4660,14 @@
           <t xml:space="preserve">Abnormal lymphocytes/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E145"/>
+      <c r="F145"/>
+      <c r="G145"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2920,6 +4685,26 @@
           <t xml:space="preserve">MCV [Entitic mean volume] in Red Blood Cells</t>
         </is>
       </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">787-2　MCV [Entitic mean volume] in Red Blood Cells by Automated count</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: MCV calculation</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2937,6 +4722,14 @@
           <t xml:space="preserve">Monocytes Abnormal/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E147"/>
+      <c r="F147"/>
+      <c r="G147"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2954,6 +4747,14 @@
           <t xml:space="preserve">Promonocytes/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E148"/>
+      <c r="F148"/>
+      <c r="G148"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2971,6 +4772,14 @@
           <t xml:space="preserve">Lymphocytes Plasmacytoid/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E149"/>
+      <c r="F149"/>
+      <c r="G149"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2988,6 +4797,14 @@
           <t xml:space="preserve">Monocytes/Leukocytes in Blood by Automated count</t>
         </is>
       </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E150"/>
+      <c r="F150"/>
+      <c r="G150"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3005,6 +4822,18 @@
           <t xml:space="preserve">Megakaryocytes/Leukocytes in Blood</t>
         </is>
       </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E151"/>
+      <c r="F151"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29 JOB-01 批3 Q7：完整巨核細胞碼（本即 IG 原欲表達者）；批2 之 70028-6=Megakaryocytic nuclei（細胞核）、62858-6=Micromegakaryocytes（微小巨核細胞）均非完整巨核細胞，故換用 19252-6；顯示名依 CI 回報之官方字串（原寫 /100 leukocytes，官方為 /Leukocytes）</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3022,6 +4851,14 @@
           <t xml:space="preserve">Basophils/Leukocytes in Blood by Automated count</t>
         </is>
       </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E152"/>
+      <c r="F152"/>
+      <c r="G152"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3039,6 +4876,14 @@
           <t xml:space="preserve">Eosinophils/Leukocytes in Blood by Automated count</t>
         </is>
       </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E153"/>
+      <c r="F153"/>
+      <c r="G153"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3056,6 +4901,14 @@
           <t xml:space="preserve">Lymphocytes [#/volume] in Blood by Automated count</t>
         </is>
       </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E154"/>
+      <c r="F154"/>
+      <c r="G154"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3073,6 +4926,14 @@
           <t xml:space="preserve">Neutrophils [#/volume] in Blood by Automated count</t>
         </is>
       </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E155"/>
+      <c r="F155"/>
+      <c r="G155"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3090,6 +4951,14 @@
           <t xml:space="preserve">MCH [Entitic mass] by Automated count</t>
         </is>
       </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E156"/>
+      <c r="F156"/>
+      <c r="G156"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3107,6 +4976,14 @@
           <t xml:space="preserve">MCHC [Entitic Mass/volume] in Red Blood Cells by Automated count</t>
         </is>
       </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E157"/>
+      <c r="F157"/>
+      <c r="G157"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3124,6 +5001,14 @@
           <t xml:space="preserve">MCV [Entitic mean volume] in Red Blood Cells by Automated count</t>
         </is>
       </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E158"/>
+      <c r="F158"/>
+      <c r="G158"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3141,6 +5026,14 @@
           <t xml:space="preserve">Erythrocyte [DistWidth] in Blood by Automated count</t>
         </is>
       </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E159"/>
+      <c r="F159"/>
+      <c r="G159"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3158,6 +5051,26 @@
           <t xml:space="preserve">Leukocytes [#/volume] in Blood by Manual count</t>
         </is>
       </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6690-2　Leukocytes [#/volume] in Blood by Automated count</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: WBC Manual</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3175,6 +5088,14 @@
           <t xml:space="preserve">Calcium [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E161"/>
+      <c r="F161"/>
+      <c r="G161"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3192,6 +5113,14 @@
           <t xml:space="preserve">Insulin [Units/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E162"/>
+      <c r="F162"/>
+      <c r="G162"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3209,6 +5138,18 @@
           <t xml:space="preserve">Homocysteine [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E163"/>
+      <c r="F163"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29 JOB-01 批2：官方為質量濃度（Q2-4）；院內以 µmol/L 莫耳報告，莫耳碼 13965-9 為檢驗醫學部建議優先</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3226,6 +5167,18 @@
           <t xml:space="preserve">Homocysteine [Moles/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E164"/>
+      <c r="F164"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">檢驗醫學部建議優先之莫耳碼（µmol/L, Q2-4）；CI 已覆核六軸相符</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3243,6 +5196,14 @@
           <t xml:space="preserve">C reactive protein [Mass/volume] in Serum or Plasma by High sensitivity method</t>
         </is>
       </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E165"/>
+      <c r="F165"/>
+      <c r="G165"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3260,6 +5221,14 @@
           <t xml:space="preserve">Urate [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E166"/>
+      <c r="F166"/>
+      <c r="G166"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3277,6 +5246,14 @@
           <t xml:space="preserve">Cystatin C [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E167"/>
+      <c r="F167"/>
+      <c r="G167"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3294,6 +5271,26 @@
           <t xml:space="preserve">Glomerular filtration rate [Volume Rate/Area] in Serum or Plasma by Creatinine-based formula (MDRD)/1.73 sq M</t>
         </is>
       </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98979-8　Glomerular filtration rate [Volume Rate/Area] in Serum, Plasma or Blood by Creatinine-based formula (CKD-EPI 2021)/1.73 sq M</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: MDRD eGFR；經 ConceptMap 歸一至 98979-8（#relatedto，不同估算公式）。2026-07-29 JOB-01 批2：批1 誤用舊式長名，依 display-verification-report.csv 官方字串更正（注意檢體軸為 Serum or Plasma，與 98979-8 之 Serum, Plasma or Blood 不同）</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3311,6 +5308,14 @@
           <t xml:space="preserve">Hemoglobin A1c/Hemoglobin.total in Blood</t>
         </is>
       </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E169"/>
+      <c r="F169"/>
+      <c r="G169"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3328,6 +5333,14 @@
           <t xml:space="preserve">Homeostasis model assessment</t>
         </is>
       </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E170"/>
+      <c r="F170"/>
+      <c r="G170"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3345,6 +5358,26 @@
           <t xml:space="preserve">Hemoglobin A1c/Hemoglobin.total standardized per IFCC-RMP for CDT in Blood</t>
         </is>
       </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4548-4　Hemoglobin A1c/Hemoglobin.total in Blood</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: HbA1c IFCC</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3362,6 +5395,14 @@
           <t xml:space="preserve">Glomerular filtration rate [Volume Rate/Area] in Serum, Plasma or Blood by Creatinine-based formula (CKD-EPI 2021)/1.73 sq M</t>
         </is>
       </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E172"/>
+      <c r="F172"/>
+      <c r="G172"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3379,6 +5420,14 @@
           <t xml:space="preserve">Globulin [Mass/volume] in Serum by calculation</t>
         </is>
       </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E173"/>
+      <c r="F173"/>
+      <c r="G173"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3396,6 +5445,26 @@
           <t xml:space="preserve">Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by With P-5'-P</t>
         </is>
       </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1742-6　Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: ALT with P-5'-P（2026-07-26 換碼，原 14390-9 實為透析液澱粉酶）</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3413,6 +5482,26 @@
           <t xml:space="preserve">Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by With P-5'-P</t>
         </is>
       </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920-8　Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: AST with P-5'-P（2026-07-26 換碼，原 14409-7 檢體為胸膜液）</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3430,6 +5519,14 @@
           <t xml:space="preserve">Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E176"/>
+      <c r="F176"/>
+      <c r="G176"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3447,6 +5544,26 @@
           <t xml:space="preserve">Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
         </is>
       </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1742-6　Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: ALT 無 P-5'-P 添加法；經 ConceptMap 歸一至 1742-6</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3464,6 +5581,14 @@
           <t xml:space="preserve">Albumin [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E178"/>
+      <c r="F178"/>
+      <c r="G178"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3481,6 +5606,14 @@
           <t xml:space="preserve">Albumin/Globulin [Mass Ratio] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E179"/>
+      <c r="F179"/>
+      <c r="G179"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3498,6 +5631,14 @@
           <t xml:space="preserve">Amylase [Enzymatic activity/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E180"/>
+      <c r="F180"/>
+      <c r="G180"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3515,6 +5656,14 @@
           <t xml:space="preserve">Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E181"/>
+      <c r="F181"/>
+      <c r="G181"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3532,6 +5681,14 @@
           <t xml:space="preserve">Bilirubin.direct [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E182"/>
+      <c r="F182"/>
+      <c r="G182"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3549,6 +5706,14 @@
           <t xml:space="preserve">Bilirubin.total [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E183"/>
+      <c r="F183"/>
+      <c r="G183"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3566,6 +5731,14 @@
           <t xml:space="preserve">Lactate dehydrogenase [Enzymatic activity/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E184"/>
+      <c r="F184"/>
+      <c r="G184"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3583,6 +5756,14 @@
           <t xml:space="preserve">Protein [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E185"/>
+      <c r="F185"/>
+      <c r="G185"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3600,6 +5781,14 @@
           <t xml:space="preserve">Lipase [Enzymatic activity/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E186"/>
+      <c r="F186"/>
+      <c r="G186"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3617,6 +5806,14 @@
           <t xml:space="preserve">Alkaline phosphatase [Enzymatic activity/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E187"/>
+      <c r="F187"/>
+      <c r="G187"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3634,6 +5831,26 @@
           <t xml:space="preserve">Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
         </is>
       </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920-8　Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: AST 無 P-5'-P 添加法；經 ConceptMap 歸一至 1920-8</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3651,6 +5868,18 @@
           <t xml:space="preserve">Cholesterol in VLDL [Mass/volume] in Serum or Plasma by calculation</t>
         </is>
       </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E189"/>
+      <c r="F189"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-26 換碼，原 46986-6 實為 VLDL 3 次分群</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -3668,6 +5897,14 @@
           <t xml:space="preserve">Cholesterol.total/Cholesterol in HDL [Mass Ratio] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E190"/>
+      <c r="F190"/>
+      <c r="G190"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3685,6 +5922,14 @@
           <t xml:space="preserve">Cobalamin (Vitamin B12) [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E191"/>
+      <c r="F191"/>
+      <c r="G191"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3702,6 +5947,14 @@
           <t xml:space="preserve">Folate [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E192"/>
+      <c r="F192"/>
+      <c r="G192"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3719,6 +5972,26 @@
           <t xml:space="preserve">Thyrotropin [Units/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11580-8　Thyrotropin [Units/volume] in Serum or Plasma by Detection limit &lt;= 0.005 mIU/L</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrower</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: TSH 3rd gen</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3736,6 +6009,14 @@
           <t xml:space="preserve">Thyroxine (T4) [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E194"/>
+      <c r="F194"/>
+      <c r="G194"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3753,6 +6034,14 @@
           <t xml:space="preserve">Triiodothyronine (T3) free [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E195"/>
+      <c r="F195"/>
+      <c r="G195"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3770,6 +6059,14 @@
           <t xml:space="preserve">Triiodothyronine (T3) [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E196"/>
+      <c r="F196"/>
+      <c r="G196"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3787,6 +6084,14 @@
           <t xml:space="preserve">25-Hydroxyvitamin D3+25-Hydroxyvitamin D2 [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E197"/>
+      <c r="F197"/>
+      <c r="G197"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3804,6 +6109,14 @@
           <t xml:space="preserve">Thyroperoxidase Ab [Units/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E198"/>
+      <c r="F198"/>
+      <c r="G198"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -3821,6 +6134,14 @@
           <t xml:space="preserve">Hepatitis A virus IgM Ab [Presence] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E199"/>
+      <c r="F199"/>
+      <c r="G199"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3838,6 +6159,14 @@
           <t xml:space="preserve">Hepatitis B virus core Ab [Presence] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E200"/>
+      <c r="F200"/>
+      <c r="G200"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3855,6 +6184,14 @@
           <t xml:space="preserve">Helicobacter pylori Ag [Presence] in Stool by Immunoassay</t>
         </is>
       </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E201"/>
+      <c r="F201"/>
+      <c r="G201"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -3872,6 +6209,14 @@
           <t xml:space="preserve">Reagin Ab [Presence] in Serum by RPR</t>
         </is>
       </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E202"/>
+      <c r="F202"/>
+      <c r="G202"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -3889,6 +6234,14 @@
           <t xml:space="preserve">Human papilloma virus 16+18+31+33+35+45+51+52+56 DNA [Presence] in Cervix by Probe</t>
         </is>
       </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E203"/>
+      <c r="F203"/>
+      <c r="G203"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -3906,6 +6259,18 @@
           <t xml:space="preserve">Hepatitis B virus surface Ab [Presence] in Serum</t>
         </is>
       </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E204"/>
+      <c r="F204"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29 JOB-01 批2：官方為定性（Q3 回覆定量+定性併報，須將對調之標示改回正確位置）</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -3923,6 +6288,14 @@
           <t xml:space="preserve">Treponema pallidum Ab [Presence] in Serum by Immunoassay</t>
         </is>
       </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E205"/>
+      <c r="F205"/>
+      <c r="G205"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3940,6 +6313,18 @@
           <t xml:space="preserve">Hemoglobin [Presence] in Stool from gastrointestinal lower by Immunoassay</t>
         </is>
       </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E206"/>
+      <c r="F206"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">糞便免疫化學法潛血(FIT)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -3957,6 +6342,14 @@
           <t xml:space="preserve">Reagin Ab [Titer] in Serum by RPR</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E207"/>
+      <c r="F207"/>
+      <c r="G207"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -3974,6 +6367,18 @@
           <t xml:space="preserve">Helicobacter pylori IgG Ab [Units/volume] in Serum by Immunoassay</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E208"/>
+      <c r="F208"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29 JOB-01 Q4-1 裁示（使用者提供 LOINC 官方查詢）：本碼官方為定量（Scale Qn、Method IA），舊標 [Presence] 有誤；本院未執行此項故無臨床背書，惟採 LOINC 官方定量顯示名保留（open-issues T-1 選項 b）</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -3991,6 +6396,14 @@
           <t xml:space="preserve">Hepatitis A virus IgG+IgM Ab [Presence] in Serum</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E209"/>
+      <c r="F209"/>
+      <c r="G209"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4008,6 +6421,18 @@
           <t xml:space="preserve">Hepatitis B virus surface Ab [Units/volume] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E210"/>
+      <c r="F210"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29 JOB-01 批2：官方為定量（Q3，標示對調回正確位置）——本碼即定量 Anti-HBs；臨床建議之 65633-0 經 CI 查證實為 HBsAg（表面「抗原」）確認法、非 Anti-HBs（抗體），已剔除</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4025,6 +6450,14 @@
           <t xml:space="preserve">Rubella virus IgG Ab [Units/volume] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E211"/>
+      <c r="F211"/>
+      <c r="G211"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4042,6 +6475,14 @@
           <t xml:space="preserve">Varicella zoster virus IgG Ab [Units/volume] in Serum by Immunoassay</t>
         </is>
       </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E212"/>
+      <c r="F212"/>
+      <c r="G212"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4059,6 +6500,14 @@
           <t xml:space="preserve">HIV 1+2 Ab+HIV1 p24 Ag [Presence] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E213"/>
+      <c r="F213"/>
+      <c r="G213"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4076,6 +6525,14 @@
           <t xml:space="preserve">Measles virus IgG Ab [Units/volume] in Serum</t>
         </is>
       </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E214"/>
+      <c r="F214"/>
+      <c r="G214"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4093,6 +6550,14 @@
           <t xml:space="preserve">Microalbumin [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E215"/>
+      <c r="F215"/>
+      <c r="G215"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4110,6 +6575,14 @@
           <t xml:space="preserve">Epithelial cells.squamous [#/area] in Urine sediment by Microscopy high power field</t>
         </is>
       </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E216"/>
+      <c r="F216"/>
+      <c r="G216"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4127,6 +6600,14 @@
           <t xml:space="preserve">Phosphate crystals amorphous [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E217"/>
+      <c r="F217"/>
+      <c r="G217"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4144,6 +6625,14 @@
           <t xml:space="preserve">Urate crystals amorphous [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E218"/>
+      <c r="F218"/>
+      <c r="G218"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4161,6 +6650,14 @@
           <t xml:space="preserve">Urobilinogen [Presence] in Urine</t>
         </is>
       </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E219"/>
+      <c r="F219"/>
+      <c r="G219"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4178,6 +6675,14 @@
           <t xml:space="preserve">Erythrocytes [#/area] in Urine sediment by Microscopy high power field</t>
         </is>
       </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E220"/>
+      <c r="F220"/>
+      <c r="G220"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4195,6 +6700,14 @@
           <t xml:space="preserve">Fungi.yeastlike [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E221"/>
+      <c r="F221"/>
+      <c r="G221"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4212,6 +6725,14 @@
           <t xml:space="preserve">Albumin/Creatinine [Mass Ratio] in Urine by Test strip</t>
         </is>
       </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E222"/>
+      <c r="F222"/>
+      <c r="G222"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4229,6 +6750,18 @@
           <t xml:space="preserve">Color of Urine</t>
         </is>
       </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E223"/>
+      <c r="F223"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-26 換碼，原 20627-6 實為尿液濁度 (Turbidity)</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4246,6 +6779,14 @@
           <t xml:space="preserve">Bacteria [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E224"/>
+      <c r="F224"/>
+      <c r="G224"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4263,6 +6804,14 @@
           <t xml:space="preserve">Creatinine [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E225"/>
+      <c r="F225"/>
+      <c r="G225"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4280,6 +6829,14 @@
           <t xml:space="preserve">Yeast [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E226"/>
+      <c r="F226"/>
+      <c r="G226"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4297,6 +6854,18 @@
           <t xml:space="preserve">Bacteria [#/volume] in Urine by Automated count</t>
         </is>
       </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E227"/>
+      <c r="F227"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 33218-9</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4314,6 +6883,26 @@
           <t xml:space="preserve">Bacteria [#/area] in Urine sediment by Automated count</t>
         </is>
       </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51480-2　Bacteria [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：每高倍視野（/HPF）鏡檢沉渣計數；以 /HPF 報告之機構適用，經 ConceptMap 歸一至 51480-2</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4331,6 +6920,18 @@
           <t xml:space="preserve">Epithelial cells.squamous [#/volume] in Urine by Automated count</t>
         </is>
       </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E229"/>
+      <c r="F229"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 33219-7</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4348,6 +6949,26 @@
           <t xml:space="preserve">Epithelial cells.squamous [#/area] in Urine sediment by Automated count</t>
         </is>
       </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51486-9　Epithelial cells.squamous [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：每高倍視野（/HPF）鏡檢沉渣計數；以 /HPF 報告之機構適用，經 ConceptMap 歸一至 51486-9</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4365,6 +6986,18 @@
           <t xml:space="preserve">Hyaline casts [#/volume] in Urine by Automated count</t>
         </is>
       </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E231"/>
+      <c r="F231"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 33223-9</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4382,6 +7015,26 @@
           <t xml:space="preserve">Hyaline casts [#/area] in Urine sediment by Automated count</t>
         </is>
       </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51484-4　Hyaline casts [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：每高倍視野（/HPF）鏡檢沉渣計數；以 /HPF 報告之機構適用，經 ConceptMap 歸一至 51484-4</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4399,6 +7052,18 @@
           <t xml:space="preserve">Epithelial cells [#/volume] in Urine by Automated</t>
         </is>
       </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E233"/>
+      <c r="F233"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 33342-7（通用上皮細胞）</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4416,6 +7081,26 @@
           <t xml:space="preserve">Epithelial cells [#/area] in Urine sediment by Automated count</t>
         </is>
       </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87926-2　Epithelial cells [#/volume] in Urine by Automated</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：每高倍視野（/HPF）鏡檢沉渣計數；以 /HPF 報告之機構適用，經 ConceptMap 歸一至 87926-2</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4433,6 +7118,18 @@
           <t xml:space="preserve">Casts [#/volume] in Urine by Automated count</t>
         </is>
       </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E235"/>
+      <c r="F235"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 43755-8</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4450,6 +7147,26 @@
           <t xml:space="preserve">Casts [#/area] in Urine sediment by Automated count</t>
         </is>
       </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51483-6　Casts [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：每高倍視野（/HPF）鏡檢沉渣計數；以 /HPF 報告之機構適用，經 ConceptMap 歸一至 51483-6</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4467,6 +7184,18 @@
           <t xml:space="preserve">Erythrocytes [#/volume] in Urine by Automated count</t>
         </is>
       </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E237"/>
+      <c r="F237"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 46419-8</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4484,6 +7213,26 @@
           <t xml:space="preserve">Erythrocytes [#/area] in Urine sediment by Automated count</t>
         </is>
       </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">798-9　Erythrocytes [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：每高倍視野（/HPF）鏡檢沉渣計數；以 /HPF 報告之機構適用，經 ConceptMap 歸一至 798-9</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4501,6 +7250,18 @@
           <t xml:space="preserve">Leukocytes [#/volume] in Urine by Automated count</t>
         </is>
       </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E239"/>
+      <c r="F239"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 46702-7</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4518,6 +7279,26 @@
           <t xml:space="preserve">Leukocytes [#/area] in Urine sediment by Automated count</t>
         </is>
       </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51487-7　Leukocytes [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：每高倍視野（/HPF）鏡檢沉渣計數；以 /HPF 報告之機構適用，經 ConceptMap 歸一至 51487-7</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4535,6 +7316,18 @@
           <t xml:space="preserve">Mucus [#/volume] in Urine by Automated count</t>
         </is>
       </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E241"/>
+      <c r="F241"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 50235-1</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4552,6 +7345,26 @@
           <t xml:space="preserve">Mucus [#/area] in Urine sediment by Automated count</t>
         </is>
       </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51478-6　Mucus [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：每高倍視野（/HPF）鏡檢沉渣計數；以 /HPF 報告之機構適用，經 ConceptMap 歸一至 51478-6</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4569,6 +7382,14 @@
           <t xml:space="preserve">Bilirubin.total [Presence] in Urine by Automated test strip</t>
         </is>
       </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E243"/>
+      <c r="F243"/>
+      <c r="G243"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4586,6 +7407,14 @@
           <t xml:space="preserve">Glucose [Presence] in Urine by Automated test strip</t>
         </is>
       </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E244"/>
+      <c r="F244"/>
+      <c r="G244"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4603,6 +7432,14 @@
           <t xml:space="preserve">Nitrite [Presence] in Urine by Automated test strip</t>
         </is>
       </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E245"/>
+      <c r="F245"/>
+      <c r="G245"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4620,6 +7457,14 @@
           <t xml:space="preserve">pH of Urine by Automated test strip</t>
         </is>
       </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E246"/>
+      <c r="F246"/>
+      <c r="G246"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4637,6 +7482,14 @@
           <t xml:space="preserve">Specific gravity of Urine by Refractometry automated</t>
         </is>
       </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E247"/>
+      <c r="F247"/>
+      <c r="G247"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4654,6 +7507,18 @@
           <t xml:space="preserve">Spermatozoa [#/volume] in Urine by Automated count</t>
         </is>
       </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E248"/>
+      <c r="F248"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29 JOB-01 批3 Q1（缺口已解，使用者提供）：51479-4 為精子之全尿自動計數體積碼（同屬套組 50554-5），比照其餘 8 項換體積碼；← 53324-0（原用每面積碼有誤）</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4671,6 +7536,26 @@
           <t xml:space="preserve">Spermatozoa [#/area] in Urine sediment by Automated count</t>
         </is>
       </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51479-4　Spermatozoa [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：每高倍視野（/HPF）鏡檢沉渣計數；以 /HPF 報告之機構適用，經 ConceptMap 歸一至 51479-4</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4688,6 +7573,14 @@
           <t xml:space="preserve">Drug crystals [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E250"/>
+      <c r="F250"/>
+      <c r="G250"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4705,6 +7598,14 @@
           <t xml:space="preserve">Ammonium urate crystals [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E251"/>
+      <c r="F251"/>
+      <c r="G251"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -4722,6 +7623,14 @@
           <t xml:space="preserve">Bilirubin.total [Presence] in Urine by Test strip</t>
         </is>
       </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E252"/>
+      <c r="F252"/>
+      <c r="G252"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -4739,6 +7648,14 @@
           <t xml:space="preserve">Bilirubin crystals [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E253"/>
+      <c r="F253"/>
+      <c r="G253"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -4756,6 +7673,14 @@
           <t xml:space="preserve">Calcium carbonate crystals [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E254"/>
+      <c r="F254"/>
+      <c r="G254"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -4773,6 +7698,14 @@
           <t xml:space="preserve">Ketones [Presence] in Urine by Automated test strip</t>
         </is>
       </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E255"/>
+      <c r="F255"/>
+      <c r="G255"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -4790,6 +7723,14 @@
           <t xml:space="preserve">Calcium oxalate crystals [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E256"/>
+      <c r="F256"/>
+      <c r="G256"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -4807,6 +7748,14 @@
           <t xml:space="preserve">Calcium phosphate crystals [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E257"/>
+      <c r="F257"/>
+      <c r="G257"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -4824,6 +7773,14 @@
           <t xml:space="preserve">Hemoglobin [Presence] in Urine by Automated test strip</t>
         </is>
       </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E258"/>
+      <c r="F258"/>
+      <c r="G258"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -4841,6 +7798,14 @@
           <t xml:space="preserve">Cholesterol crystals [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E259"/>
+      <c r="F259"/>
+      <c r="G259"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -4858,6 +7823,14 @@
           <t xml:space="preserve">Cystine crystals [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E260"/>
+      <c r="F260"/>
+      <c r="G260"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -4875,6 +7848,14 @@
           <t xml:space="preserve">Epithelial cells [#/area] in Urine sediment by Microscopy high power field</t>
         </is>
       </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E261"/>
+      <c r="F261"/>
+      <c r="G261"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -4892,6 +7873,14 @@
           <t xml:space="preserve">Oval fat bodies (globules) [#/area] in Urine sediment by Microscopy high power field</t>
         </is>
       </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E262"/>
+      <c r="F262"/>
+      <c r="G262"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -4909,6 +7898,14 @@
           <t xml:space="preserve">Glucose [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E263"/>
+      <c r="F263"/>
+      <c r="G263"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -4926,6 +7923,14 @@
           <t xml:space="preserve">Hemoglobin [Presence] in Urine by Test strip</t>
         </is>
       </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E264"/>
+      <c r="F264"/>
+      <c r="G264"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -4943,6 +7948,14 @@
           <t xml:space="preserve">Hyaline casts [#/area] in Urine sediment by Microscopy low power field</t>
         </is>
       </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E265"/>
+      <c r="F265"/>
+      <c r="G265"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -4960,6 +7973,14 @@
           <t xml:space="preserve">Ketones [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E266"/>
+      <c r="F266"/>
+      <c r="G266"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -4977,6 +7998,14 @@
           <t xml:space="preserve">Leukocyte esterase [Presence] in Urine by Test strip</t>
         </is>
       </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E267"/>
+      <c r="F267"/>
+      <c r="G267"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -4994,6 +8023,14 @@
           <t xml:space="preserve">Nitrite [Presence] in Urine by Test strip</t>
         </is>
       </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E268"/>
+      <c r="F268"/>
+      <c r="G268"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -5011,6 +8048,14 @@
           <t xml:space="preserve">pH of Urine by Test strip</t>
         </is>
       </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E269"/>
+      <c r="F269"/>
+      <c r="G269"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5028,6 +8073,14 @@
           <t xml:space="preserve">Trichomonas vaginalis [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E270"/>
+      <c r="F270"/>
+      <c r="G270"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -5045,6 +8098,14 @@
           <t xml:space="preserve">Triple phosphate crystals [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E271"/>
+      <c r="F271"/>
+      <c r="G271"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -5062,6 +8123,14 @@
           <t xml:space="preserve">Urate crystals [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E272"/>
+      <c r="F272"/>
+      <c r="G272"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5079,6 +8148,14 @@
           <t xml:space="preserve">Leukocytes [#/area] in Urine sediment by Microscopy high power field</t>
         </is>
       </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E273"/>
+      <c r="F273"/>
+      <c r="G273"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -5096,6 +8173,14 @@
           <t xml:space="preserve">Leukocyte esterase [Presence] in Urine by Automated test strip</t>
         </is>
       </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E274"/>
+      <c r="F274"/>
+      <c r="G274"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5113,6 +8198,14 @@
           <t xml:space="preserve">Urobilinogen [Presence] in Urine by Automated test strip</t>
         </is>
       </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E275"/>
+      <c r="F275"/>
+      <c r="G275"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5130,6 +8223,18 @@
           <t xml:space="preserve">Albumin/Creatinine [Mass Ratio] in Urine</t>
         </is>
       </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E276"/>
+      <c r="F276"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-26 換碼，原 13705-9 檢體為 24 小時尿；⚠️ 待確認：健檢 ACR 若驗微白蛋白應改用 14959-1（Microalbumin/Creatinine）</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5147,6 +8252,14 @@
           <t xml:space="preserve">Microalbumin [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E277"/>
+      <c r="F277"/>
+      <c r="G277"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -5164,6 +8277,14 @@
           <t xml:space="preserve">C reactive protein [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E278"/>
+      <c r="F278"/>
+      <c r="G278"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -5181,6 +8302,14 @@
           <t xml:space="preserve">Creatinine [Mass/volume] in Urine</t>
         </is>
       </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E279"/>
+      <c r="F279"/>
+      <c r="G279"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -5198,6 +8327,14 @@
           <t xml:space="preserve">Hemoglobin H/Hemoglobin.total in Blood</t>
         </is>
       </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E280"/>
+      <c r="F280"/>
+      <c r="G280"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -5215,6 +8352,14 @@
           <t xml:space="preserve">Ova and parasites identified in Stool by Concentration</t>
         </is>
       </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E281"/>
+      <c r="F281"/>
+      <c r="G281"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -5232,6 +8377,14 @@
           <t xml:space="preserve">Ova and parasites identified in Stool by Light microscopy</t>
         </is>
       </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E282"/>
+      <c r="F282"/>
+      <c r="G282"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -5249,6 +8402,14 @@
           <t xml:space="preserve">Leukocytes [Presence] in Stool by Light microscopy</t>
         </is>
       </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E283"/>
+      <c r="F283"/>
+      <c r="G283"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -5266,6 +8427,14 @@
           <t xml:space="preserve">Hemoglobin [Presence] in Stool from gastrointestinal</t>
         </is>
       </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E284"/>
+      <c r="F284"/>
+      <c r="G284"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -5283,6 +8452,14 @@
           <t xml:space="preserve">Erythrocytes [Presence] in Stool</t>
         </is>
       </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E285"/>
+      <c r="F285"/>
+      <c r="G285"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5300,6 +8477,14 @@
           <t xml:space="preserve">Mucus [Presence] in Stool by Light microscopy</t>
         </is>
       </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E286"/>
+      <c r="F286"/>
+      <c r="G286"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5317,6 +8502,14 @@
           <t xml:space="preserve">Color of Stool</t>
         </is>
       </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E287"/>
+      <c r="F287"/>
+      <c r="G287"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -5334,6 +8527,26 @@
           <t xml:space="preserve">Forced vital capacity [Volume] Respiratory system by Spirometry --pre bronchodilation</t>
         </is>
       </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19868-9　Forced vital capacity [Volume] Respiratory system by Spirometry</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FVC (Acceptable：支氣管擴張劑前特定碼)</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5349,6 +8562,1373 @@
       <c r="C289" t="inlineStr">
         <is>
           <t xml:space="preserve">Visual acuity panel</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（單一碼）</t>
+        </is>
+      </c>
+      <c r="E289"/>
+      <c r="F289"/>
+      <c r="G289"/>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="58" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="58" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="6" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source display</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target display</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">equivalence</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">804-5</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leukocytes [#/volume] in Blood by Manual count</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6690-2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leukocytes [#/volume] in Blood by Automated count</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual 與 Automated 為不同具體方法，無包含關係；數值不可直接比較（比照 element[5] 之處理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26464-8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leukocytes [#/volume] in Blood</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6690-2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leukocytes [#/volume] in Blood by Automated count</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrower</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 方法未指定，target 指定 Automated count；target 語意較窄</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2339-0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glucose [Mass/volume] in Blood</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1558-6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fasting glucose [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">空腹狀態與檢體均不同（source 為未指定空腹之全血、target 為空腹血漿），無包含關係；全血與血漿葡萄糖數值不可直接比較（比照 element[5] 之處理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38483-4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Creatinine [Mass/volume] in Blood</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2160-0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Creatinine [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">檢體不同(Blood vs Serum/Plasma)，非包含關係</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35200-5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cholesterol [Mass or Moles/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2093-3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cholesterol [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrower</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 允許質量或莫耳濃度兩種尺度，語意較 target 廣</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3043-7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triglyceride [Mass/volume] in Blood</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2571-8</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triglyceride [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">檢體不同(Blood vs Serum/Plasma)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13457-7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by calculation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2089-1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定計算法，target 方法未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33914-3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glomerular filtration rate [Volume Rate/Area] in Serum or Plasma by Creatinine-based formula (MDRD)/1.73 sq M</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98979-8</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glomerular filtration rate [Volume Rate/Area] in Serum, Plasma or Blood by Creatinine-based formula (CKD-EPI 2021)/1.73 sq M</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MDRD 與 CKD-EPI 2021 為不同估算公式，數值不可直接互換。114 年成健採雙軌併行（MDRD 必填、CKD-EPI 非必填），同一份報告可能同時含兩碼，屬正常情形而非重複上傳；115.01.01 起僅採 CKD-EPI 2021。依國健署 115.01.15 國健慢病字第1150660003號函。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5195-3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5196-1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 限 Serum、target 為 Serum or Plasma 且指定 Immunoassay，兩者互有寬窄</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16128-1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13955-0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 限 Serum、target 為 Serum or Plasma 且指定 Immunoassay，兩者互有寬窄</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26515-7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platelets [#/volume] in Blood</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777-3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platelets [#/volume] in Blood by Automated count</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrower</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 方法未指定，target 指定 Automated count；target 語意較窄</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30428-7</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MCV [Entitic mean volume] in Red Blood Cells</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">787-2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MCV [Entitic mean volume] in Red Blood Cells by Automated count</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">calculation 與 Automated count 為不同具體方法，無包含關係</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28539-5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MCH [Entitic mass]</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">785-6</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MCH [Entitic mass] by Automated count</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrower</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 方法未指定（MCH [Entitic mass]），target 指定 Automated count；target 語意較窄</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26508-2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neutrophils/100 leukocytes in Blood by Manual count</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">770-8</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neutrophils/Leukocytes in Blood by Automated count</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual 與 Automated 為不同具體方法，無包含關係</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30239-8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by With P-5'-P</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920-8</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定 UV with P5P，target 方法未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1743-4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by With P-5'-P</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1742-6</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定 UV with P5P，target 方法未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59261-8</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hemoglobin A1c/Hemoglobin.total standardized per IFCC-RMP for CDT in Blood</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4548-4</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hemoglobin A1c/Hemoglobin.total in Blood</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit conversion required: NGSP(%) = IFCC(mmol/mol) * 0.9148 + 2.152</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3016-3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thyrotropin [Units/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11580-8</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thyrotropin [Units/volume] in Serum or Plasma by Detection limit &lt;= 0.005 mIU/L</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrower</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為一般 TSH（未指定偵測極限），target 指定高敏感度（Detection limit &lt;= 0.005 mIU/L）；target 語意較窄</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83082-8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cancer Ag 125 [Units/volume] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10334-1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cancer Ag 125 [Units/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定 Immunoassay，target 方法未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83085-1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carcinoembryonic Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2039-6</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carcinoembryonic Ag [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定 Immunoassay，target 方法未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88112-8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920-8</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定 No addition of P-5'-P，target 方法未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1744-2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1742-6</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定 No addition of P-5'-P，target 方法未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2345-7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glucose [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1558-6</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fasting Glucose [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrower</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為未指定空腹狀態之一般血糖，語意較 target(空腹)廣</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18262-6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by Direct assay</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2089-1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定 Direct assay，target 方法未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23749-5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead [Mass/volume] in Specimen</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77307-7</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead [Mass/volume] in Venous blood</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 檢體為泛稱 Specimen、target 限 Blood，非單純包含</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56086-2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waist Circumference</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8280-0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waist Circumference at umbilicus by Tape measure</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為 PhenX 之量測 protocol 碼、target 為臍位皮尺量測碼，性質不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5671-3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead [Mass/volume] in Blood</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77307-7</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead [Mass/volume] in Venous blood</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 之檢體為未指定之 Blood、target 限 Venous blood；職業血鉛監測慣用靜脈血。source 之 LOINC 狀態為 DISCOURAGED。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33218-9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bacteria [#/area] in Urine sediment by Automated count</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51480-2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bacteria [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為每高倍視野（/HPF）鏡檢沉渣計數、target 為每體積（/µL）全尿自動計數；兩者需依儀器換算係數（離心速度、沉渣濃縮倍率、視野面積）轉換，不可直接比較數值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33219-7</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Epithelial cells.squamous [#/area] in Urine sediment by Automated count</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51486-9</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Epithelial cells.squamous [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為每高倍視野（/HPF）鏡檢沉渣計數、target 為每體積（/µL）全尿自動計數；兩者需依儀器換算係數（離心速度、沉渣濃縮倍率、視野面積）轉換，不可直接比較數值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33223-9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hyaline casts [#/area] in Urine sediment by Automated count</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51484-4</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hyaline casts [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為每高倍視野（/HPF）鏡檢沉渣計數、target 為每體積（/µL）全尿自動計數；兩者需依儀器換算係數（離心速度、沉渣濃縮倍率、視野面積）轉換，不可直接比較數值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33342-7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Epithelial cells [#/area] in Urine sediment by Automated count</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87926-2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Epithelial cells [#/volume] in Urine by Automated</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為每高倍視野（/HPF）鏡檢沉渣計數、target 為每體積（/µL）全尿自動計數；兩者需依儀器換算係數（離心速度、沉渣濃縮倍率、視野面積）轉換，不可直接比較數值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43755-8</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Casts [#/area] in Urine sediment by Automated count</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51483-6</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Casts [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為每高倍視野（/HPF）鏡檢沉渣計數、target 為每體積（/µL）全尿自動計數；兩者需依儀器換算係數（離心速度、沉渣濃縮倍率、視野面積）轉換，不可直接比較數值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46419-8</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erythrocytes [#/area] in Urine sediment by Automated count</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">798-9</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erythrocytes [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為每高倍視野（/HPF）鏡檢沉渣計數、target 為每體積（/µL）全尿自動計數；兩者需依儀器換算係數（離心速度、沉渣濃縮倍率、視野面積）轉換，不可直接比較數值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46702-7</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leukocytes [#/area] in Urine sediment by Automated count</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51487-7</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leukocytes [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為每高倍視野（/HPF）鏡檢沉渣計數、target 為每體積（/µL）全尿自動計數；兩者需依儀器換算係數（離心速度、沉渣濃縮倍率、視野面積）轉換，不可直接比較數值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50235-1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mucus [#/area] in Urine sediment by Automated count</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51478-6</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mucus [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為每高倍視野（/HPF）鏡檢沉渣計數、target 為每體積（/µL）全尿自動計數；兩者需依儀器換算係數（離心速度、沉渣濃縮倍率、視野面積）轉換，不可直接比較數值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53324-0</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spermatozoa [#/area] in Urine sediment by Automated count</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51479-4</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spermatozoa [#/volume] in Urine by Automated count</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為每高倍視野（/HPF）鏡檢沉渣計數、target 為每體積（/µL）全尿自動計數；兩者需依儀器換算係數（離心速度、沉渣濃縮倍率、視野面積）轉換，不可直接比較數值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3137-7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Body height Measured</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8302-2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Body height</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定量測方法（Method = Measured），target 方法未指定；二者為同一身高量測概念之方法特化與通用，屬包含關係，數值可直接比較。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3141-9</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Body weight Measured</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29463-7</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Body weight</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定量測方法（Method = Measured），target 方法未指定；二者為同一體重量測概念之方法特化與通用，屬包含關係，數值可直接比較。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57735-3</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Presence] in Urine by Automated test strip</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定自動化試紙判讀，target 方法未指定自動化；target 語意較廣</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63557-3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Units/volume] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5196-1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為定量（Units/volume）、target 為定性（Presence），Property 不同而無包含關係；定量值不可直接當作定性結果比較，須依判讀閾值轉換</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19876-2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forced vital capacity [Volume] Respiratory system by Spirometry --pre bronchodilation</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19868-9</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forced vital capacity [Volume] Respiratory system by Spirometry</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定支氣管擴張劑給藥前之特定條件，target 未指定給藥前後；target 語意較廣</t>
         </is>
       </c>
     </row>

--- a/input/assets/loinc-valuesets.xlsx
+++ b/input/assets/loinc-valuesets.xlsx
@@ -321,42 +321,54 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">09043C 高密度脂蛋白膽固醇 (HDL-C) — Preferred 2085-9</t>
+          <t xml:space="preserve">09004C 三酸甘油酯 (Triglyceride) — Preferred 2571-8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085-9</t>
+          <t xml:space="preserve">3048-6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholesterol in HDL [Mass/volume] in Serum or Plasma</t>
+          <t xml:space="preserve">Triglyceride [Mass/volume] in Serum or Plasma --fasting</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2571-8　Triglyceride [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：空腹採檢條件特化（2026-08-22 委員決議補回——健檢實務確為空腹採檢）；經 ConceptMap 歸一至 2571-8（#wider）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">09044C 低密度脂蛋白膽固醇 (LDL-C) — Preferred 2089-1（**方法通用碼**：tx 確認其官方顯示名未指定方法，</t>
+          <t xml:space="preserve">09043C 高密度脂蛋白膽固醇 (HDL-C) — Preferred 2085-9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089-1</t>
+          <t xml:space="preserve">2085-9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
+          <t xml:space="preserve">Cholesterol in HDL [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -376,34 +388,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">13457-7</t>
+          <t xml:space="preserve">2089-1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by calculation</t>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2089-1　Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wider</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Acceptable: 計算法</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">18262-6</t>
+          <t xml:space="preserve">13457-7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by Direct assay</t>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by calculation</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -438,34 +438,46 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable: 直接法舊碼</t>
+          <t xml:space="preserve">Acceptable: 計算法</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">09015C 肌酸酐 (Creatinine) — Preferred 2160-0</t>
+          <t xml:space="preserve">09044C 低密度脂蛋白膽固醇 (LDL-C) — Preferred 2089-1（**方法通用碼**：tx 確認其官方顯示名未指定方法，</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160-0</t>
+          <t xml:space="preserve">18262-6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Creatinine [Mass/volume] in Serum or Plasma</t>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by Direct assay</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2089-1　Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 直接法舊碼</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -475,74 +487,74 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">38483-4</t>
+          <t xml:space="preserve">2160-0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Creatinine [Mass/volume] in Blood</t>
+          <t xml:space="preserve">Creatinine [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2160-0　Creatinine [Mass/volume] in Serum or Plasma</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Acceptable: 全血法</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">06003C 尿蛋白定量 (Urine Protein, quantitative) — Preferred 2888-6</t>
+          <t xml:space="preserve">09015C 肌酸酐 (Creatinine) — Preferred 2160-0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2888-6</t>
+          <t xml:space="preserve">38483-4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protein [Mass/volume] in Urine</t>
+          <t xml:space="preserve">Creatinine [Mass/volume] in Blood</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2160-0　Creatinine [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 全血法</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">06003C 尿蛋白定性 (Urine Protein, qualitative) — Preferred 5804-0</t>
+          <t xml:space="preserve">06003C 尿蛋白定量 (Urine Protein, quantitative) — Preferred 2888-6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5804-0</t>
+          <t xml:space="preserve">2888-6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -562,59 +574,59 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57735-3</t>
+          <t xml:space="preserve">5804-0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protein [Presence] in Urine by Automated test strip</t>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wider</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Acceptable: 試紙變異碼</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+          <t xml:space="preserve">06003C 尿蛋白定性 (Urine Protein, qualitative) — Preferred 5804-0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196-1</t>
+          <t xml:space="preserve">57735-3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">Protein [Presence] in Urine by Automated test strip</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 試紙變異碼（Ord/PrThr，與 Preferred 之 SemiQn/MCnc 跨 Scale，屬上開明文例外）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -624,34 +636,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195-3</t>
+          <t xml:space="preserve">5196-1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum</t>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5196-1　Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Acceptable: 血清定性(原22326-3 經tx驗證實為 HCV 5-1-1 Ab，已更正)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">63557-3</t>
+          <t xml:space="preserve">5195-3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis B virus surface Ag [Units/volume] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -686,34 +686,46 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable: 免疫法</t>
+          <t xml:space="preserve">Acceptable: 血清定性(原22326-3 經tx驗證實為 HCV 5-1-1 Ab，已更正)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">14051C C型肝炎抗體 (anti-HCV) — Preferred 13955-0</t>
+          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">13955-0</t>
+          <t xml:space="preserve">63557-3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Units/volume] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5196-1　Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 免疫法</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -723,30 +735,55 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t xml:space="preserve">13955-0</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14051C C型肝炎抗體 (anti-HCV) — Preferred 13955-0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t xml:space="preserve">16128-1</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">Acceptable</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">13955-0　Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">Acceptable: 血清通用碼（原 47365-2 為捐血者篩檢情境碼，不適用一般健檢，已更正）</t>
         </is>
@@ -9932,6 +9969,134 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3048-6</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triglyceride [Mass/volume] in Serum or Plasma --fasting</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2571-8</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triglyceride [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定空腹採檢條件，target 未指定空腹；target 語意較廣。數值可直接比較，惟歸一後會遺失「空腹」之條件標示，接收端如需區分應保留原始 coding。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8281-8</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waist Circumference at umbilicus by US</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8280-0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waist Circumference at umbilicus by Tape measure</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為超音波量測、target 為臍位皮尺量測；兩者為同層之方法兄弟碼而非通用與特化之包含關係，量測原理不同，數值不可直接等同比較。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56114-2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waist Circumference by NHANES</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8280-0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waist Circumference at umbilicus by Tape measure</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為 NHANES 之量測 protocol 碼、target 為臍位皮尺量測碼，性質不同（比照 element[25] 之 PhenX protocol 碼）。本碼不納入任何值集，僅供接收端歸一。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56115-9</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waist Circumference by NCFS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8280-0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waist Circumference at umbilicus by Tape measure</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為 NCFS 之量測 protocol 碼、target 為臍位皮尺量測碼，性質不同（比照 element[25] 之 PhenX protocol 碼）。本碼不納入任何值集，僅供接收端歸一。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/input/assets/loinc-valuesets.xlsx
+++ b/input/assets/loinc-valuesets.xlsx
@@ -358,42 +358,54 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">09043C 高密度脂蛋白膽固醇 (HDL-C) — Preferred 2085-9</t>
+          <t xml:space="preserve">09004C 三酸甘油酯 (Triglyceride) — Preferred 2571-8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085-9</t>
+          <t xml:space="preserve">1644-4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholesterol in HDL [Mass/volume] in Serum or Plasma</t>
+          <t xml:space="preserve">Triglyceride [Mass/volume] in Serum or Plasma --12 hours fasting</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2571-8　Triglyceride [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：12 小時空腹條件特化（2026-08-22 第二批委員決議）；經 ConceptMap 歸一至 2571-8（#wider）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">09044C 低密度脂蛋白膽固醇 (LDL-C) — Preferred 2089-1（**方法通用碼**：tx 確認其官方顯示名未指定方法，</t>
+          <t xml:space="preserve">09043C 高密度脂蛋白膽固醇 (HDL-C) — Preferred 2085-9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089-1</t>
+          <t xml:space="preserve">2085-9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
+          <t xml:space="preserve">Cholesterol in HDL [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -413,34 +425,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">13457-7</t>
+          <t xml:space="preserve">2089-1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by calculation</t>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2089-1　Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wider</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Acceptable: 計算法</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">18262-6</t>
+          <t xml:space="preserve">13457-7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by Direct assay</t>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by calculation</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -475,34 +475,46 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable: 直接法舊碼</t>
+          <t xml:space="preserve">Acceptable: 計算法</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">09015C 肌酸酐 (Creatinine) — Preferred 2160-0</t>
+          <t xml:space="preserve">09044C 低密度脂蛋白膽固醇 (LDL-C) — Preferred 2089-1（**方法通用碼**：tx 確認其官方顯示名未指定方法，</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160-0</t>
+          <t xml:space="preserve">18262-6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Creatinine [Mass/volume] in Serum or Plasma</t>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by Direct assay</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2089-1　Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 直接法舊碼</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -512,74 +524,74 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">38483-4</t>
+          <t xml:space="preserve">2160-0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Creatinine [Mass/volume] in Blood</t>
+          <t xml:space="preserve">Creatinine [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2160-0　Creatinine [Mass/volume] in Serum or Plasma</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Acceptable: 全血法</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">06003C 尿蛋白定量 (Urine Protein, quantitative) — Preferred 2888-6</t>
+          <t xml:space="preserve">09015C 肌酸酐 (Creatinine) — Preferred 2160-0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2888-6</t>
+          <t xml:space="preserve">38483-4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protein [Mass/volume] in Urine</t>
+          <t xml:space="preserve">Creatinine [Mass/volume] in Blood</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2160-0　Creatinine [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 全血法</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">06003C 尿蛋白定性 (Urine Protein, qualitative) — Preferred 5804-0</t>
+          <t xml:space="preserve">06003C 尿蛋白定量 (Urine Protein, quantitative) — Preferred 2888-6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5804-0</t>
+          <t xml:space="preserve">2888-6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -599,74 +611,74 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">57735-3</t>
+          <t xml:space="preserve">5804-0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protein [Presence] in Urine by Automated test strip</t>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wider</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Acceptable: 試紙變異碼（Ord/PrThr，與 Preferred 之 SemiQn/MCnc 跨 Scale，屬上開明文例外）</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+          <t xml:space="preserve">06003C 尿蛋白定性 (Urine Protein, qualitative) — Preferred 5804-0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196-1</t>
+          <t xml:space="preserve">57735-3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">Protein [Presence] in Urine by Automated test strip</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 試紙變異碼（Ord/PrThr，與 Preferred 之 SemiQn/MCnc 跨 Scale，屬上開明文例外）</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+          <t xml:space="preserve">06003C 尿蛋白定性 (Urine Protein, qualitative) — Preferred 5804-0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195-3</t>
+          <t xml:space="preserve">50561-0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum</t>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Automated test strip</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -676,34 +688,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196-1　Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+          <t xml:space="preserve">wider</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable: 血清定性(原22326-3 經tx驗證實為 HCV 5-1-1 Ab，已更正)</t>
+          <t xml:space="preserve">Acceptable：自動化試紙（2026-08-22 第二批委員決議）；Property 與 Scale 均與 Preferred 相同，僅 Method 特化，**不跨 Scale**；經 ConceptMap 歸一至 5804-0（#wider）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+          <t xml:space="preserve">06003C 尿蛋白定性 (Urine Protein, qualitative) — Preferred 5804-0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">63557-3</t>
+          <t xml:space="preserve">2887-8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis B virus surface Ag [Units/volume] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">Protein [Presence] in Urine</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -713,7 +725,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196-1　Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -723,67 +735,203 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable: 免疫法</t>
+          <t xml:space="preserve">Acceptable：定性通用碼（2026-08-22 第二批委員決議）；Ord/PrThr，跨 Scale；經 ConceptMap 歸一至 5804-0（#relatedto——無包含關係，須依判讀閾值轉換）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">14051C C型肝炎抗體 (anti-HCV) — Preferred 13955-0</t>
+          <t xml:space="preserve">06003C 尿蛋白定性 (Urine Protein, qualitative) — Preferred 5804-0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">13955-0</t>
+          <t xml:space="preserve">20454-5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">Protein [Presence] in Urine by Test strip</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：定性試紙碼（2026-08-22 第二批委員決議）；Ord/PrThr，跨 Scale；經 ConceptMap 歸一至 5804-0（#relatedto，同上）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5196-1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5195-3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5196-1　Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 血清定性(原22326-3 經tx驗證實為 HCV 5-1-1 Ab，已更正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63557-3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Units/volume] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5196-1　Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 免疫法</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t xml:space="preserve">14051C C型肝炎抗體 (anti-HCV) — Preferred 13955-0</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13955-0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14051C C型肝炎抗體 (anti-HCV) — Preferred 13955-0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t xml:space="preserve">16128-1</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">Acceptable</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">13955-0　Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">Acceptable: 血清通用碼（原 47365-2 為捐血者篩檢情境碼，不適用一般健檢，已更正）</t>
         </is>
@@ -10097,6 +10245,134 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1644-4</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triglyceride [Mass/volume] in Serum or Plasma --12 hours fasting</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2571-8</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triglyceride [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定 12 小時空腹條件，target 未指定空腹；target 語意較廣。數值可直接比較，惟歸一後會遺失空腹時數之標示，接收端如需區分應保留原始 coding。與 element[41]（3048-6 --fasting）同型，差別僅在本碼明指 12 小時。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50561-0</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Automated test strip</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定自動化試紙判讀，target 方法未指定自動化；Property（MCnc）與 Scale（SemiQn）均與 target 相同，僅 Method 特化，屬包含關係，數值可直接比較。本組未跨 Scale，與 element[47]／[48] 不同。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2887-8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Presence] in Urine</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為定性（Property = PrThr、Scale = Ord、方法未指定）、target 為半定量（MCnc / SemiQn、試紙法）；Property 與 Scale 均不同而無包含關係，定性結果不可直接當作半定量分級比較，須依判讀閾值轉換。比照 element[39]（63557-3 定量 → 5196-1 定性）之處理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20454-5</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Presence] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為定性（PrThr / Ord）、target 為半定量（MCnc / SemiQn）；Method 雖同為試紙法，惟 Property 與 Scale 不同而無包含關係，須依判讀閾值轉換。同 element[47] 之判準。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/input/assets/loinc-valuesets.xlsx
+++ b/input/assets/loinc-valuesets.xlsx
@@ -656,12 +656,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">wider</t>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable: 試紙變異碼（Ord/PrThr，與 Preferred 之 SemiQn/MCnc 跨 Scale，屬上開明文例外）</t>
+          <t xml:space="preserve">Acceptable：自動化試紙定性碼；Ord/PrThr，跨 Scale；經 ConceptMap 歸一至 5804-0（#relatedto——v0.10.2 由 #wider 更正，見下註）</t>
         </is>
       </c>
     </row>
@@ -10044,12 +10044,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">wider</t>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">source 指定自動化試紙判讀，target 方法未指定自動化；target 語意較廣</t>
+          <t xml:space="preserve">source 為定性（Property = PrThr、Scale = Ord、自動化試紙）、target 為半定量（MCnc / SemiQn、試紙法）；Property 與 Scale 均不同而無包含關係，定性結果不可直接當作半定量分級比較，須依判讀閾值轉換。⚠️ v0.10.2 更正：本組原標 wider，其 comment 僅描述 Method 一軸（「source 指定自動化試紙判讀，target 方法未指定自動化」），漏看 Property 與 Scale 亦不相同。判準與 element[47]／[48]（2887-8／20454-5）完全相同，故一併改為 relatedto。</t>
         </is>
       </c>
     </row>

--- a/input/assets/loinc-valuesets.xlsx
+++ b/input/assets/loinc-valuesets.xlsx
@@ -358,42 +358,54 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">09043C 高密度脂蛋白膽固醇 (HDL-C) — Preferred 2085-9</t>
+          <t xml:space="preserve">09004C 三酸甘油酯 (Triglyceride) — Preferred 2571-8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085-9</t>
+          <t xml:space="preserve">1644-4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholesterol in HDL [Mass/volume] in Serum or Plasma</t>
+          <t xml:space="preserve">Triglyceride [Mass/volume] in Serum or Plasma --12 hours fasting</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2571-8　Triglyceride [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：12 小時空腹條件特化（2026-08-22 第二批委員決議）；經 ConceptMap 歸一至 2571-8（#wider）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">09044C 低密度脂蛋白膽固醇 (LDL-C) — Preferred 2089-1（**方法通用碼**：tx 確認其官方顯示名未指定方法，</t>
+          <t xml:space="preserve">09043C 高密度脂蛋白膽固醇 (HDL-C) — Preferred 2085-9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089-1</t>
+          <t xml:space="preserve">2085-9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
+          <t xml:space="preserve">Cholesterol in HDL [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -413,34 +425,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">13457-7</t>
+          <t xml:space="preserve">2089-1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by calculation</t>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2089-1　Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wider</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Acceptable: 計算法</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">18262-6</t>
+          <t xml:space="preserve">13457-7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by Direct assay</t>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by calculation</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -475,34 +475,46 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable: 直接法舊碼</t>
+          <t xml:space="preserve">Acceptable: 計算法</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">09015C 肌酸酐 (Creatinine) — Preferred 2160-0</t>
+          <t xml:space="preserve">09044C 低密度脂蛋白膽固醇 (LDL-C) — Preferred 2089-1（**方法通用碼**：tx 確認其官方顯示名未指定方法，</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160-0</t>
+          <t xml:space="preserve">18262-6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Creatinine [Mass/volume] in Serum or Plasma</t>
+          <t xml:space="preserve">Cholesterol in LDL [Mass/volume] in Serum or Plasma by Direct assay</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2089-1　Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 直接法舊碼</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -512,74 +524,74 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">38483-4</t>
+          <t xml:space="preserve">2160-0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Creatinine [Mass/volume] in Blood</t>
+          <t xml:space="preserve">Creatinine [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2160-0　Creatinine [Mass/volume] in Serum or Plasma</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Acceptable: 全血法</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">06003C 尿蛋白定量 (Urine Protein, quantitative) — Preferred 2888-6</t>
+          <t xml:space="preserve">09015C 肌酸酐 (Creatinine) — Preferred 2160-0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2888-6</t>
+          <t xml:space="preserve">38483-4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protein [Mass/volume] in Urine</t>
+          <t xml:space="preserve">Creatinine [Mass/volume] in Blood</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2160-0　Creatinine [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 全血法</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">06003C 尿蛋白定性 (Urine Protein, qualitative) — Preferred 5804-0</t>
+          <t xml:space="preserve">06003C 尿蛋白定量 (Urine Protein, quantitative) — Preferred 2888-6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5804-0</t>
+          <t xml:space="preserve">2888-6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -599,74 +611,74 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">57735-3</t>
+          <t xml:space="preserve">5804-0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protein [Presence] in Urine by Automated test strip</t>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wider</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Acceptable: 試紙變異碼（Ord/PrThr，與 Preferred 之 SemiQn/MCnc 跨 Scale，屬上開明文例外）</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+          <t xml:space="preserve">06003C 尿蛋白定性 (Urine Protein, qualitative) — Preferred 5804-0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196-1</t>
+          <t xml:space="preserve">57735-3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">Protein [Presence] in Urine by Automated test strip</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：自動化試紙定性碼；Ord/PrThr，跨 Scale；經 ConceptMap 歸一至 5804-0（#relatedto——v0.10.2 由 #wider 更正，見下註）</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+          <t xml:space="preserve">06003C 尿蛋白定性 (Urine Protein, qualitative) — Preferred 5804-0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195-3</t>
+          <t xml:space="preserve">50561-0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum</t>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Automated test strip</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -676,34 +688,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196-1　Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+          <t xml:space="preserve">wider</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable: 血清定性(原22326-3 經tx驗證實為 HCV 5-1-1 Ab，已更正)</t>
+          <t xml:space="preserve">Acceptable：自動化試紙（2026-08-22 第二批委員決議）；Property 與 Scale 均與 Preferred 相同，僅 Method 特化，**不跨 Scale**；經 ConceptMap 歸一至 5804-0（#wider）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+          <t xml:space="preserve">06003C 尿蛋白定性 (Urine Protein, qualitative) — Preferred 5804-0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">63557-3</t>
+          <t xml:space="preserve">2887-8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis B virus surface Ag [Units/volume] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">Protein [Presence] in Urine</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -713,7 +725,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196-1　Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -723,67 +735,203 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acceptable: 免疫法</t>
+          <t xml:space="preserve">Acceptable：定性通用碼（2026-08-22 第二批委員決議）；Ord/PrThr，跨 Scale；經 ConceptMap 歸一至 5804-0（#relatedto——無包含關係，須依判讀閾值轉換）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">14051C C型肝炎抗體 (anti-HCV) — Preferred 13955-0</t>
+          <t xml:space="preserve">06003C 尿蛋白定性 (Urine Protein, qualitative) — Preferred 5804-0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">13955-0</t>
+          <t xml:space="preserve">20454-5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
+          <t xml:space="preserve">Protein [Presence] in Urine by Test strip</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preferred</t>
-        </is>
-      </c>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0　Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable：定性試紙碼（2026-08-22 第二批委員決議）；Ord/PrThr，跨 Scale；經 ConceptMap 歸一至 5804-0（#relatedto，同上）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5196-1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5195-3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Presence] in Serum</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5196-1　Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 血清定性(原22326-3 經tx驗證實為 HCV 5-1-1 Ab，已更正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14032C B型肝炎表面抗原 (HBsAg) — Preferred 5196-1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63557-3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis B virus surface Ag [Units/volume] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5196-1　Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptable: 免疫法</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t xml:space="preserve">14051C C型肝炎抗體 (anti-HCV) — Preferred 13955-0</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13955-0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferred</t>
+        </is>
+      </c>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14051C C型肝炎抗體 (anti-HCV) — Preferred 13955-0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t xml:space="preserve">16128-1</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t xml:space="preserve">Hepatitis C virus Ab [Presence] in Serum</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">Acceptable</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">13955-0　Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">Acceptable: 血清通用碼（原 47365-2 為捐血者篩檢情境碼，不適用一般健檢，已更正）</t>
         </is>
@@ -9896,12 +10044,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">wider</t>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">source 指定自動化試紙判讀，target 方法未指定自動化；target 語意較廣</t>
+          <t xml:space="preserve">source 為定性（Property = PrThr、Scale = Ord、自動化試紙）、target 為半定量（MCnc / SemiQn、試紙法）；Property 與 Scale 均不同而無包含關係，定性結果不可直接當作半定量分級比較，須依判讀閾值轉換。⚠️ v0.10.2 更正：本組原標 wider，其 comment 僅描述 Method 一軸（「source 指定自動化試紙判讀，target 方法未指定自動化」），漏看 Property 與 Scale 亦不相同。判準與 element[47]／[48]（2887-8／20454-5）完全相同，故一併改為 relatedto。</t>
         </is>
       </c>
     </row>
@@ -10094,6 +10242,134 @@
       <c r="F46" t="inlineStr">
         <is>
           <t xml:space="preserve">source 為 NCFS 之量測 protocol 碼、target 為臍位皮尺量測碼，性質不同（比照 element[25] 之 PhenX protocol 碼）。本碼不納入任何值集，僅供接收端歸一。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1644-4</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triglyceride [Mass/volume] in Serum or Plasma --12 hours fasting</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2571-8</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triglyceride [Mass/volume] in Serum or Plasma</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定 12 小時空腹條件，target 未指定空腹；target 語意較廣。數值可直接比較，惟歸一後會遺失空腹時數之標示，接收端如需區分應保留原始 coding。與 element[41]（3048-6 --fasting）同型，差別僅在本碼明指 12 小時。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50561-0</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Automated test strip</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wider</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 指定自動化試紙判讀，target 方法未指定自動化；Property（MCnc）與 Scale（SemiQn）均與 target 相同，僅 Method 特化，屬包含關係，數值可直接比較。本組未跨 Scale，與 element[47]／[48] 不同。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2887-8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Presence] in Urine</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為定性（Property = PrThr、Scale = Ord、方法未指定）、target 為半定量（MCnc / SemiQn、試紙法）；Property 與 Scale 均不同而無包含關係，定性結果不可直接當作半定量分級比較，須依判讀閾值轉換。比照 element[39]（63557-3 定量 → 5196-1 定性）之處理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20454-5</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Presence] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5804-0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein [Mass/volume] in Urine by Test strip</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source 為定性（PrThr / Ord）、target 為半定量（MCnc / SemiQn）；Method 雖同為試紙法，惟 Property 與 Scale 不同而無包含關係，須依判讀閾值轉換。同 element[47] 之判準。</t>
         </is>
       </c>
     </row>

--- a/input/assets/loinc-valuesets.xlsx
+++ b/input/assets/loinc-valuesets.xlsx
@@ -4882,7 +4882,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+          <t xml:space="preserve">narrower</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠ relatedto（需換算，數值不可直接比較）</t>
+          <t xml:space="preserve">narrower</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">calculation 與 Automated count 為不同具體方法，無包含關係</t>
+          <t xml:space="preserve">source 方法未指定，target 指定 Automated count；target 語意較窄。⚠️ v0.10.3 更正：本組原標 relatedto，comment 為「calculation 與 Automated count 為不同具體方法，無包含關係」——惟 30428-7 之 METHOD_TYP 於 LOINC 實為**未指定**，並非 calculation，該 comment 主張了 source 不具備的方法。六軸與 element[10]（26515-7 → 777-3）及 element[12]（28539-5 → 785-6）完全相同，該二組皆標 narrower。⚠️ 對實作端之影響：該組之「數值可否直接比較」由「不可」翻為**可**——同一量測之方法通用碼與 Automated count 特化碼屬包含關係，先前依 relatedto 而不予比較者可改為直接比較。</t>
         </is>
       </c>
     </row>
